--- a/templates/intake/catalog.xlsx
+++ b/templates/intake/catalog.xlsx
@@ -728,7 +728,7 @@
         <v>2550000</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="3">
